--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.7.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.7.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -987,7 +987,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.7.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.7.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y48"/>
+  <dimension ref="A1:Y47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -581,15 +581,19 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00126_19130805\oocihm.N_00126_19130805.7.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00126_19130805\oocihm.N_00126_19130805.7.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.7.txt</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr"/>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.7.txt</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>L43: suspicious token(s): 79c (letter/digit mix), 89c (letter/digit mix), 98c (letter/digit mix) | possible duplicated/overlap line with previous line (similarity 62%) :: Ladies Underskirts, Special at 79c., 89c., 98c., $ 1.00, $ 1.10</t>
+        </is>
+      </c>
       <c r="E2" s="1" t="inlineStr"/>
       <c r="F2" s="1" t="inlineStr">
         <is>
@@ -613,16 +617,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L42: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 79c (letter/digit mix), 89c (letter/digit mix) :: Ladiesâ€™White Princess Slips, Special at 79c., 89c. and $1.69.</t>
+          <t>L94: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L46: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L21: isolated marker/symbol line :: 14</t>
@@ -630,7 +638,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -640,13 +648,13 @@
       </c>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>L107: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” TO ---</t>
+          <t>L107: punctuation artifact: double/multiple hyphen :: — TO ---</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L289: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | line starts with digit/letter garbage token | suspicious token(s): 0Photo (letter/digit mix) :: 0Photoâ€™s COPHRIETESLIN 6^</t>
+          <t>L289: line starts with digit/letter garbage token | suspicious token(s): 0Photo’s (letter/digit mix) :: 0Photo’s COPHRIETESLIN 6^</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -681,7 +689,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>668</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -704,12 +712,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L49: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Shop early Thursdayâ€”Store closes at o'clock.</t>
+          <t>L647: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: These exhibitions ， no doubt are</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L57: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L46: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -785,14 +793,10 @@
           <t>L102: suspicious token(s): 79c (letter/digit mix), 98c (letter/digit mix) :: Ladies' Night Gowns, high and low neck, Special at 79c., 98c., $1.00</t>
         </is>
       </c>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: WANTED â€” TO</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L57: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -810,7 +814,7 @@
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L231: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€”DENTI STS. ------</t>
+          <t>L231: punctuation artifact: double/multiple hyphen :: —DENTI STS. ------</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
@@ -838,12 +842,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>68</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>66</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -856,7 +860,7 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr">
         <is>
-          <t>L42: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 79c (letter/digit mix), 89c (letter/digit mix) :: Ladiesâ€™White Princess Slips, Special at 79c., 89c. and $1.69.</t>
+          <t>L42: suspicious token(s): 79c (letter/digit mix), 89c (letter/digit mix) :: Ladies’White Princess Slips, Special at 79c., 89c. and $1.69.</t>
         </is>
       </c>
       <c r="I5" s="1" t="inlineStr">
@@ -864,14 +868,10 @@
           <t>L105: suspicious token(s): 19c (letter/digit mix) :: Ladies' Corset Covers, nicely trimmed, Special at 19c. each.</t>
         </is>
       </c>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L65: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L63: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -895,7 +895,7 @@
       <c r="R5" s="1" t="inlineStr"/>
       <c r="S5" s="1" t="inlineStr">
         <is>
-          <t>L923: line starts with lowercase prefix glued to capitalized word | suspicious token(s): nJinternational (odd internal casing) | missing space after period :: nJinternational point of view.It assists to</t>
+          <t>L487: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • week,</t>
         </is>
       </c>
       <c r="T5" s="1" t="inlineStr"/>
@@ -935,7 +935,7 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr">
         <is>
-          <t>L43: suspicious token(s): 79c (letter/digit mix), 89c (letter/digit mix), 98c (letter/digit mix) :: Ladies Underskirts, Special at 79c., 89c., 98c., $ 1.00, $ 1.10</t>
+          <t>L43: suspicious token(s): 79c (letter/digit mix), 89c (letter/digit mix), 98c (letter/digit mix) | possible duplicated/overlap line with previous line (similarity 62%) :: Ladies Underskirts, Special at 79c., 89c., 98c., $ 1.00, $ 1.10</t>
         </is>
       </c>
       <c r="I6" s="1" t="inlineStr">
@@ -943,14 +943,10 @@
           <t>L169: suspicious token(s): U1 (letter/digit mix) | localized OCR phrase divergence vs other OCR: "" vs "1 U1 rtiinifi I ABORERS n 11" :: 1 U1</t>
         </is>
       </c>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L275: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: "Ought I to feel triumphantâ€”hap-</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L89: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN | isolated marker/symbol line :: â‚¬</t>
+          <t>L65: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -968,11 +964,15 @@
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>L826: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: hall; then he looked up and saw her -------------â€”â€”</t>
+          <t>L826: punctuation artifact: double/multiple hyphen :: hall; then he looked up and saw her -------------——</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
-      <c r="S6" s="1" t="inlineStr"/>
+      <c r="S6" s="1" t="inlineStr">
+        <is>
+          <t>L923: line starts with lowercase prefix glued to capitalized word | suspicious token(s): nJinternational (odd internal casing) | missing space after period :: nJinternational point of view.It assists to</t>
+        </is>
+      </c>
       <c r="T6" s="1" t="inlineStr"/>
       <c r="U6" s="1" t="inlineStr"/>
       <c r="V6" s="1" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
@@ -1015,17 +1015,13 @@
       </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
-          <t>L289: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | line starts with digit/letter garbage token | suspicious token(s): 0Photo (letter/digit mix) :: 0Photoâ€™s COPHRIETESLIN 6^</t>
-        </is>
-      </c>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L281: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œDo</t>
-        </is>
-      </c>
+          <t>L289: line starts with digit/letter garbage token | suspicious token(s): 0Photo’s (letter/digit mix) :: 0Photo’s COPHRIETESLIN 6^</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L107: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” TO ---</t>
+          <t>L89: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: €</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
@@ -1037,7 +1033,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L46: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L46: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -1089,14 +1085,10 @@
           <t>L479: line starts with lowercase prefix glued to capitalized word | suspicious token(s): tGam (odd internal casing) :: tGam-</t>
         </is>
       </c>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L351: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: one foolsâ€”ourselves exceptedâ€”â€”</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L152: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Shop early Thursday morningâ€”Store closes at 1 clock.</t>
+          <t>L167: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
@@ -1152,14 +1144,10 @@
           <t>L622: suspicious token(s): UManitoba (odd internal casing) :: UManitoba, Saskatchewan and Alberta,</t>
         </is>
       </c>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L375: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Moncton, Aug. 4.â€” Emille Pellarin,</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L167: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L487: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • week,</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
@@ -1193,12 +1181,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1215,14 +1203,10 @@
           <t>L712: suspicious token(s): seen1should (letter/digit mix) :: yes, I know him well. Haven't seen1should have to go back.</t>
         </is>
       </c>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>L395: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: DENTIST â€” Office. and</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L172: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: I - ABORERSâ€™</t>
+          <t>L804: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
@@ -1234,7 +1218,7 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L57: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L57: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1261,7 +1245,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1278,14 +1262,10 @@
           <t>L923: line starts with lowercase prefix glued to capitalized word | suspicious token(s): nJinternational (odd internal casing) | missing space after period :: nJinternational point of view.It assists to</t>
         </is>
       </c>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>L420: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: OFFICE AND RESIDENCEâ€”â€”</t>
-        </is>
-      </c>
+      <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L185: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: WANTEDâ€”Four boys to sell papers. Ap-</t>
+          <t>L922: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: enjoying it for a few years and they •,</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
@@ -1324,7 +1304,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1341,14 +1321,10 @@
           <t>L932: suspicious token(s): which1 (letter/digit mix) :: the outstanding characteristics which1'__</t>
         </is>
       </c>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>L457: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: OFFICE â€” Opp. Officers Quarters, Queen</t>
-        </is>
-      </c>
+      <c r="J12" s="1" t="inlineStr"/>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L186: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ply at Gleaner Office.â€”634d.</t>
+          <t>L975: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
@@ -1360,7 +1336,7 @@
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L63: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1396,14 +1372,10 @@
       <c r="G13" s="1" t="inlineStr"/>
       <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr"/>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>L551: stray/suspicious non-ASCII glyph(s): U+00AD SOFT HYPHEN :: mÃ­nd my leaving you. Oh, here's a</t>
-        </is>
-      </c>
+      <c r="J13" s="1" t="inlineStr"/>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>L227: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: FOR SALEâ€”Geo. Kitchen property about</t>
+          <t>L977: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: S'•</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr"/>
@@ -1415,7 +1387,7 @@
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L65: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L65: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1442,7 +1414,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1451,16 +1423,8 @@
       <c r="G14" s="1" t="inlineStr"/>
       <c r="H14" s="1" t="inlineStr"/>
       <c r="I14" s="1" t="inlineStr"/>
-      <c r="J14" s="1" t="inlineStr">
-        <is>
-          <t>L557: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: " I understand,â€� he said, as if her</t>
-        </is>
-      </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L229: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: A. B. Kitchen.â€”613d.</t>
-        </is>
-      </c>
+      <c r="J14" s="1" t="inlineStr"/>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
@@ -1506,21 +1470,13 @@
       <c r="G15" s="1" t="inlineStr"/>
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr"/>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t>L576: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: to one of the executive offices â€” than</t>
-        </is>
-      </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L231: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€”DENTI STS. ------</t>
-        </is>
-      </c>
+      <c r="J15" s="1" t="inlineStr"/>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L94: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
@@ -1561,16 +1517,8 @@
       <c r="G16" s="1" t="inlineStr"/>
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr"/>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>L618: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ã€�</t>
-        </is>
-      </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L287: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜Phone 419-11. House, 57-41.</t>
-        </is>
-      </c>
+      <c r="J16" s="1" t="inlineStr"/>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
@@ -1616,16 +1564,8 @@
       <c r="G17" s="1" t="inlineStr"/>
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>L620: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: suspicious. The expected happenedâ€”â€”</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L289: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | line starts with digit/letter garbage token | suspicious token(s): 0Photo (letter/digit mix) :: 0Photoâ€™s COPHRIETESLIN 6^</t>
-        </is>
-      </c>
+      <c r="J17" s="1" t="inlineStr"/>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
@@ -1659,16 +1599,8 @@
       <c r="G18" s="1" t="inlineStr"/>
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t>L639: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: London, Aug. 4 â€” In view of Britain's</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L293: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: always with admirationâ€”or envy."</t>
-        </is>
-      </c>
+      <c r="J18" s="1" t="inlineStr"/>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
@@ -1678,7 +1610,7 @@
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L89: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN | isolated marker/symbol line :: â‚¬</t>
+          <t>L89: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: €</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1702,16 +1634,8 @@
       <c r="G19" s="1" t="inlineStr"/>
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr"/>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t>L661: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ã€�</t>
-        </is>
-      </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L297: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: "Ought I to feel triumphantâ€”hap-</t>
-        </is>
-      </c>
+      <c r="J19" s="1" t="inlineStr"/>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
@@ -1745,16 +1669,8 @@
       <c r="G20" s="1" t="inlineStr"/>
       <c r="H20" s="1" t="inlineStr"/>
       <c r="I20" s="1" t="inlineStr"/>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>L679: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: glorious beauty â€” glorious in its youth</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L349: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: OFFICE AND RESIDENCE â€” Corner</t>
-        </is>
-      </c>
+      <c r="J20" s="1" t="inlineStr"/>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
@@ -1788,16 +1704,8 @@
       <c r="G21" s="1" t="inlineStr"/>
       <c r="H21" s="1" t="inlineStr"/>
       <c r="I21" s="1" t="inlineStr"/>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>L681: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: and freshnessâ€”and smiled.</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L366: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: us during this weekâ€™s sale.</t>
-        </is>
-      </c>
+      <c r="J21" s="1" t="inlineStr"/>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
@@ -1831,16 +1739,8 @@
       <c r="G22" s="1" t="inlineStr"/>
       <c r="H22" s="1" t="inlineStr"/>
       <c r="I22" s="1" t="inlineStr"/>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>L695: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of his â€”</t>
-        </is>
-      </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L383: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: They are unapproachableâ€”even by</t>
-        </is>
-      </c>
+      <c r="J22" s="1" t="inlineStr"/>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
@@ -1875,11 +1775,7 @@
       <c r="H23" s="1" t="inlineStr"/>
       <c r="I23" s="1" t="inlineStr"/>
       <c r="J23" s="1" t="inlineStr"/>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L418: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: and freshnessâ€”and smiled.</t>
-        </is>
-      </c>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
@@ -1914,11 +1810,7 @@
       <c r="H24" s="1" t="inlineStr"/>
       <c r="I24" s="1" t="inlineStr"/>
       <c r="J24" s="1" t="inlineStr"/>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L456: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: will leave the oâ€™1 Star Line wharf.</t>
-        </is>
-      </c>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
@@ -1953,11 +1845,7 @@
       <c r="H25" s="1" t="inlineStr"/>
       <c r="I25" s="1" t="inlineStr"/>
       <c r="J25" s="1" t="inlineStr"/>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L458: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: and Friday mornings at 8 oâ€™clock for St.</t>
-        </is>
-      </c>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
@@ -1992,11 +1880,7 @@
       <c r="H26" s="1" t="inlineStr"/>
       <c r="I26" s="1" t="inlineStr"/>
       <c r="J26" s="1" t="inlineStr"/>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L487: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ week,</t>
-        </is>
-      </c>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
@@ -2031,11 +1915,7 @@
       <c r="H27" s="1" t="inlineStr"/>
       <c r="I27" s="1" t="inlineStr"/>
       <c r="J27" s="1" t="inlineStr"/>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L508: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: BOYâ€™S INJURIES</t>
-        </is>
-      </c>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
@@ -2070,11 +1950,7 @@
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr"/>
       <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L527: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: something of Lord Dashleighâ€”every-</t>
-        </is>
-      </c>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
@@ -2109,11 +1985,7 @@
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr"/>
       <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L554: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: That isâ€”yes, it is Wilmot," said</t>
-        </is>
-      </c>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
@@ -2123,7 +1995,7 @@
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L167: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L167: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -2148,11 +2020,7 @@
       <c r="H30" s="1" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr"/>
       <c r="J30" s="1" t="inlineStr"/>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L586: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: know a way down to the bottom of the one but foolsâ€”ourselves excepted-</t>
-        </is>
-      </c>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
@@ -2187,11 +2055,7 @@
       <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="1" t="inlineStr"/>
       <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L601: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: OFFICE â€” Opp. Officersâ€™ Quarters, Queen</t>
-        </is>
-      </c>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
@@ -2226,11 +2090,7 @@
       <c r="H32" s="1" t="inlineStr"/>
       <c r="I32" s="1" t="inlineStr"/>
       <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L604: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Moncton, Aug. 4.â€”Emilie Pellarin,</t>
-        </is>
-      </c>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
@@ -2265,11 +2125,7 @@
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr"/>
       <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L672: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: N B.â€” Unauthorized publication of this</t>
-        </is>
-      </c>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
@@ -2304,11 +2160,7 @@
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr"/>
       <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L673: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: advertisement will not be paid for.â€”</t>
-        </is>
-      </c>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
@@ -2343,11 +2195,7 @@
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr"/>
       <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L680: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: lady and gentlemanâ€”the lady Italian,</t>
-        </is>
-      </c>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
@@ -2382,11 +2230,7 @@
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr"/>
       <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L686: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: illyâ€™s</t>
-        </is>
-      </c>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
@@ -2421,11 +2265,7 @@
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr"/>
       <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L767: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: quite true, you know. But he went mind my leaving youâ€”. Oh, hereâ€™s a</t>
-        </is>
-      </c>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
@@ -2460,16 +2300,12 @@
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr"/>
       <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L773: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: find Gerald and tell him thatâ€”</t>
-        </is>
-      </c>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L618: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ã€�</t>
+          <t>L618: isolated marker/symbol line :: 、</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
@@ -2499,16 +2335,12 @@
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr"/>
       <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L804: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L661: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ã€�</t>
+          <t>L661: isolated marker/symbol line :: 、</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr">
@@ -2538,11 +2370,7 @@
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr"/>
       <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L826: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: hall; then he looked up and saw her -------------â€”â€”</t>
-        </is>
-      </c>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
@@ -2577,11 +2405,7 @@
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr"/>
       <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L855: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: "Charlie" Foster, as he is familiar naments on skirtâ€”Maison Paquin,</t>
-        </is>
-      </c>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
@@ -2591,7 +2415,7 @@
       </c>
       <c r="O41" s="1" t="inlineStr">
         <is>
-          <t>L804: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L804: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P41" s="1" t="inlineStr"/>
@@ -2616,11 +2440,7 @@
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr"/>
       <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L859: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: I London, Aug. 4â€”In view of Britainâ€™s</t>
-        </is>
-      </c>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
@@ -2655,11 +2475,7 @@
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr"/>
       <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L906: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Canadian Pacific at St. John,â€™ and in</t>
-        </is>
-      </c>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
@@ -2694,11 +2510,7 @@
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr"/>
       <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L913: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: resting place of the C. P. R.â€™s best</t>
-        </is>
-      </c>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
@@ -2733,17 +2545,13 @@
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr"/>
       <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L922: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: enjoying it for a few years and they â€¢,</t>
-        </is>
-      </c>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr"/>
       <c r="O45" s="1" t="inlineStr">
         <is>
-          <t>L975: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
+          <t>L975: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="P45" s="1" t="inlineStr"/>
@@ -2768,17 +2576,13 @@
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr"/>
       <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L956: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Ask for Wilsonâ€™s, be sure</t>
-        </is>
-      </c>
+      <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr"/>
       <c r="O46" s="1" t="inlineStr">
         <is>
-          <t>L983: isolated marker/symbol line :: I</t>
+          <t>L977: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: S'•</t>
         </is>
       </c>
       <c r="P46" s="1" t="inlineStr"/>
@@ -2803,15 +2607,15 @@
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr"/>
       <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L975: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
-        </is>
-      </c>
+      <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr"/>
-      <c r="O47" s="1" t="inlineStr"/>
+      <c r="O47" s="1" t="inlineStr">
+        <is>
+          <t>L983: isolated marker/symbol line :: I</t>
+        </is>
+      </c>
       <c r="P47" s="1" t="inlineStr"/>
       <c r="Q47" s="1" t="inlineStr"/>
       <c r="R47" s="1" t="inlineStr"/>
@@ -2823,37 +2627,6 @@
       <c r="X47" s="1" t="inlineStr"/>
       <c r="Y47" s="1" t="inlineStr"/>
     </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr"/>
-      <c r="B48" s="1" t="inlineStr"/>
-      <c r="C48" s="1" t="inlineStr"/>
-      <c r="D48" s="1" t="inlineStr"/>
-      <c r="E48" s="1" t="inlineStr"/>
-      <c r="F48" s="1" t="inlineStr"/>
-      <c r="G48" s="1" t="inlineStr"/>
-      <c r="H48" s="1" t="inlineStr"/>
-      <c r="I48" s="1" t="inlineStr"/>
-      <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L977: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: S'â€¢</t>
-        </is>
-      </c>
-      <c r="L48" s="1" t="inlineStr"/>
-      <c r="M48" s="1" t="inlineStr"/>
-      <c r="N48" s="1" t="inlineStr"/>
-      <c r="O48" s="1" t="inlineStr"/>
-      <c r="P48" s="1" t="inlineStr"/>
-      <c r="Q48" s="1" t="inlineStr"/>
-      <c r="R48" s="1" t="inlineStr"/>
-      <c r="S48" s="1" t="inlineStr"/>
-      <c r="T48" s="1" t="inlineStr"/>
-      <c r="U48" s="1" t="inlineStr"/>
-      <c r="V48" s="1" t="inlineStr"/>
-      <c r="W48" s="1" t="inlineStr"/>
-      <c r="X48" s="1" t="inlineStr"/>
-      <c r="Y48" s="1" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
